--- a/etf_holdings/2026-10-26_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-26_00990A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:40</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,40 +504,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>NVDANVIDIA CORP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2385</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.87%406,000</t>
+          <t>5.90%280,800</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>5.90%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>406000</v>
+        <v>280800</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:40</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,40 +567,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>METAMETA PLATFORMS INC-CLASS A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.36%1085</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.14%667,000</t>
+          <t>5.37%81,400</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>5.37%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>667000</v>
+        <v>81400</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:42</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,44 +626,44 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>BEBLOOM ENERGY CORP- A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4%1560</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.99%420,000</t>
+          <t>5.13%227,500</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>420000</v>
+        <v>227500</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:42</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -689,44 +689,44 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>MSFTMICROSOFT CORP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.14%4010</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.99%165,000</t>
+          <t>4.56%90,560</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>4.56%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>165000</v>
+        <v>90560</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:42</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -752,44 +752,44 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>LITELUMENTUM HOLDINGS INC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.6%5070</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.95%134,000</t>
+          <t>4.31%53,599</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>4.31%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>134000</v>
+        <v>53599</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:42</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -815,44 +815,44 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>AMDADVANCED MICRO DEVICES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.78%3145</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.49%158,000</t>
+          <t>4.25%81,379</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>158000</v>
+        <v>81379</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:43</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -878,44 +878,44 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>PLTRPALANTIR TECHNOLOGIES INC-A</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.6%1265</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.36%348,000</t>
+          <t>4.09%214,442</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>348000</v>
+        <v>214442</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:43</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -941,11 +941,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6857ADVANTEST CORP</t>
+          <t>SPCXSPACE EXPLORATION TECHN-CL A</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -965,16 +965,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.22%59,400</t>
+          <t>3.87%256,528</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>59400</v>
+        <v>256528</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:43</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1004,44 +1004,44 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>SHOPSHOPIFY INC - CLASS A</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.69%1115</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.21%346,000</t>
+          <t>3.36%204,100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>346000</v>
+        <v>204100</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:43</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1067,44 +1067,44 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>NOWSERVICENOW INC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.19%7585</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.03%44,000</t>
+          <t>3.24%224,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>44000</v>
+        <v>224000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:43</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1130,44 +1130,44 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>SNOWSNOWFLAKE INC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.2%1775</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.02%193,000</t>
+          <t>3.09%101,200</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>193000</v>
+        <v>101200</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-26 23:20:43</t>
+          <t>2026-10-26 23:29:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,47 +1193,236 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6098RECRUIT HOLDINGS CO LTD</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>-1.45%2385</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2.87%406,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2.87%</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>406000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-26 23:29:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DDOGDATADOG INC - CLASS A</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>——</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.00%88,300</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>88300</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2.53%98,000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2.53%</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>98000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-26 23:29:22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ZSZSCALER INC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2.15%98,300</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2.15%</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>98300</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-26 23:29:22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3037欣興</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-1.36%1085</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-1.36%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2.14%667,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>667000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
